--- a/DataPreparation/Metadata/Joghurt-Haferflocken-Studie_Probandeninformationen.xlsx
+++ b/DataPreparation/Metadata/Joghurt-Haferflocken-Studie_Probandeninformationen.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="378">
   <si>
     <t>Fragebogen 1</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Studie Ende Termin 4</t>
   </si>
   <si>
-    <t>Abschlussfragebogen</t>
-  </si>
-  <si>
     <t>Studie abgeschlossen</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>J</t>
   </si>
   <si>
-    <t>PDF</t>
-  </si>
-  <si>
     <t>JH2</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>27.08.2021 12 Uhr</t>
   </si>
   <si>
-    <t>Papier</t>
-  </si>
-  <si>
     <t>JH20</t>
   </si>
   <si>
@@ -603,9 +594,6 @@
   </si>
   <si>
     <t>23.09. 17:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papier </t>
   </si>
   <si>
     <t>JH86</t>
@@ -1369,8 +1357,8 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1391,7 +1379,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1653,37 +1641,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AD128"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="1" customWidth="1"/>
-    <col min="9" max="11" width="10.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="38" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" style="38" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" style="38" customWidth="1"/>
-    <col min="17" max="17" width="13.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="38" customWidth="1"/>
-    <col min="19" max="19" width="15.88671875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" style="38" customWidth="1"/>
-    <col min="21" max="21" width="15.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="1" customWidth="1"/>
+    <col min="9" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" style="38" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="38" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" style="38" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="38" customWidth="1"/>
+    <col min="19" max="19" width="15.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" style="38" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" customWidth="1"/>
     <col min="22" max="22" width="15" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" style="1" customWidth="1"/>
     <col min="24" max="24" width="14" style="38" customWidth="1"/>
-    <col min="25" max="25" width="11.44140625" style="1"/>
-    <col min="26" max="26" width="11.44140625" style="38"/>
-    <col min="27" max="31" width="11.109375" style="34" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" style="1"/>
+    <col min="26" max="26" width="11.42578125" style="38"/>
+    <col min="27" max="30" width="11.140625" style="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="77.25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1691,7 +1679,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -1709,13 +1697,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2" t="s">
@@ -1756,26 +1744,23 @@
       <c r="Z1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="E2" s="6">
         <v>28</v>
@@ -1795,7 +1780,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
       <c r="M2" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9">
         <v>44116</v>
@@ -1803,23 +1788,23 @@
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
       <c r="Q2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R2" s="10">
         <v>44146</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="9">
         <v>44172</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V2" s="6"/>
       <c r="W2" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X2" s="10">
         <v>44209</v>
@@ -1828,26 +1813,23 @@
       <c r="Z2" s="10">
         <v>44237</v>
       </c>
-      <c r="AA2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="6"/>
       <c r="AC2" s="6"/>
       <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6">
         <v>49</v>
@@ -1867,7 +1849,7 @@
       <c r="K3" s="7"/>
       <c r="L3" s="8"/>
       <c r="M3" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N3" s="10">
         <v>44109</v>
@@ -1875,23 +1857,23 @@
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R3" s="10">
         <v>44137</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T3" s="10">
         <v>44165</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V3" s="6"/>
       <c r="W3" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X3" s="10">
         <v>44214</v>
@@ -1904,20 +1886,19 @@
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
       <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6">
         <v>36</v>
@@ -1937,19 +1918,19 @@
       <c r="K4" s="7"/>
       <c r="L4" s="8"/>
       <c r="M4" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N4" s="10">
         <v>44319</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" s="10">
         <v>44347</v>
@@ -1961,7 +1942,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X4" s="15">
         <v>44406</v>
@@ -1970,26 +1951,23 @@
       <c r="Z4" s="10">
         <v>44434</v>
       </c>
-      <c r="AA4" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA4" s="14"/>
       <c r="AB4" s="14"/>
       <c r="AC4" s="14"/>
       <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6">
         <v>41</v>
@@ -2017,19 +1995,19 @@
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N5" s="10">
         <v>44438</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R5" s="10">
         <f>N5+28</f>
@@ -2043,7 +2021,7 @@
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X5" s="15">
         <v>44523</v>
@@ -2053,26 +2031,23 @@
         <f>X5+28</f>
         <v>44551</v>
       </c>
-      <c r="AA5" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>28</v>
@@ -2092,7 +2067,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="8"/>
       <c r="M6" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N6" s="10">
         <v>44105</v>
@@ -2100,23 +2075,23 @@
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R6" s="10">
         <v>44133</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T6" s="10">
         <v>44161</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X6" s="10">
         <v>44209</v>
@@ -2125,26 +2100,23 @@
       <c r="Z6" s="10">
         <v>44238</v>
       </c>
-      <c r="AA6" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA6" s="14"/>
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
-      <c r="AE6" s="14"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="6">
         <v>28</v>
@@ -2164,17 +2136,17 @@
       <c r="K7" s="7"/>
       <c r="L7" s="8"/>
       <c r="M7" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N7" s="10">
         <v>44319</v>
       </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R7" s="10">
         <v>44347</v>
@@ -2188,7 +2160,7 @@
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X7" s="15">
         <v>44419</v>
@@ -2197,26 +2169,23 @@
       <c r="Z7" s="10">
         <v>44447</v>
       </c>
-      <c r="AA7" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA7" s="14"/>
       <c r="AB7" s="14"/>
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6">
         <v>24</v>
@@ -2244,19 +2213,19 @@
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N8" s="10">
         <v>44435</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R8" s="15">
         <v>44466</v>
@@ -2269,7 +2238,7 @@
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X8" s="10">
         <f>T8+28</f>
@@ -2280,26 +2249,23 @@
         <f>X8+28</f>
         <v>44550</v>
       </c>
-      <c r="AA8" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA8" s="14"/>
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
       <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6">
         <v>49</v>
@@ -2319,7 +2285,7 @@
       <c r="K9" s="7"/>
       <c r="L9" s="8"/>
       <c r="M9" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N9" s="10">
         <v>44109</v>
@@ -2327,23 +2293,23 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" s="10">
         <v>44134</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T9" s="10">
         <v>44161</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X9" s="10">
         <v>44207</v>
@@ -2352,26 +2318,23 @@
       <c r="Z9" s="10">
         <v>44235</v>
       </c>
-      <c r="AA9" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA9" s="14"/>
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
       <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6">
         <v>26</v>
@@ -2391,7 +2354,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="8"/>
       <c r="M10" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N10" s="10">
         <v>44111</v>
@@ -2399,23 +2362,23 @@
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R10" s="10">
         <v>44139</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T10" s="10">
         <v>44167</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V10" s="6"/>
       <c r="W10" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X10" s="10">
         <v>44207</v>
@@ -2424,26 +2387,23 @@
       <c r="Z10" s="10">
         <v>44235</v>
       </c>
-      <c r="AA10" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
-      <c r="AE10" s="14"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="6">
         <v>40</v>
@@ -2463,7 +2423,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="8"/>
       <c r="M11" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N11" s="10">
         <v>44111</v>
@@ -2471,23 +2431,23 @@
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R11" s="10">
         <v>44139</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T11" s="10">
         <v>44167</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V11" s="6"/>
       <c r="W11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X11" s="10">
         <v>44209</v>
@@ -2496,26 +2456,23 @@
       <c r="Z11" s="10">
         <v>44238</v>
       </c>
-      <c r="AA11" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="6">
         <v>39</v>
@@ -2547,13 +2504,13 @@
         <v>44435</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R12" s="10">
         <f>N12+28</f>
@@ -2567,7 +2524,7 @@
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X12" s="10">
         <f>T12+28</f>
@@ -2578,26 +2535,23 @@
         <f>X12+28</f>
         <v>44547</v>
       </c>
-      <c r="AA12" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA12" s="14"/>
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="6">
         <v>55</v>
@@ -2617,7 +2571,7 @@
       <c r="K13" s="7"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N13" s="10">
         <v>44109</v>
@@ -2625,23 +2579,23 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R13" s="10">
         <v>44137</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T13" s="10">
         <v>44165</v>
       </c>
       <c r="U13" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X13" s="10">
         <v>44207</v>
@@ -2650,26 +2604,23 @@
       <c r="Z13" s="10">
         <v>44235</v>
       </c>
-      <c r="AA13" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA13" s="14"/>
       <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
       <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="6">
         <v>53</v>
@@ -2689,7 +2640,7 @@
       <c r="K14" s="7"/>
       <c r="L14" s="17"/>
       <c r="M14" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N14" s="10">
         <v>44110</v>
@@ -2697,23 +2648,23 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R14" s="10">
         <v>44138</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T14" s="10">
         <v>44167</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V14" s="6"/>
       <c r="W14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X14" s="10">
         <v>44210</v>
@@ -2722,26 +2673,23 @@
       <c r="Z14" s="10">
         <v>44238</v>
       </c>
-      <c r="AA14" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA14" s="14"/>
       <c r="AB14" s="14"/>
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
-      <c r="AE14" s="14"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" s="6">
         <v>26</v>
@@ -2769,19 +2717,19 @@
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N15" s="10">
         <v>44435</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R15" s="10">
         <f>N15+28</f>
@@ -2794,7 +2742,7 @@
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X15" s="10">
         <f>T15+28</f>
@@ -2805,26 +2753,23 @@
         <f>X15+28</f>
         <v>44657</v>
       </c>
-      <c r="AA15" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA15" s="14"/>
       <c r="AB15" s="14"/>
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>50</v>
@@ -2852,17 +2797,17 @@
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N16" s="10">
         <v>44216</v>
       </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R16" s="10">
         <v>44246</v>
@@ -2874,7 +2819,7 @@
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X16" s="10">
         <v>44302</v>
@@ -2887,20 +2832,19 @@
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
       <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" s="6">
         <v>55</v>
@@ -2920,7 +2864,7 @@
       <c r="K17" s="7"/>
       <c r="L17" s="8"/>
       <c r="M17" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N17" s="10">
         <v>44105</v>
@@ -2928,23 +2872,23 @@
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R17" s="10">
         <v>44133</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T17" s="10">
         <v>44161</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V17" s="6"/>
       <c r="W17" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X17" s="10">
         <v>44207</v>
@@ -2957,20 +2901,19 @@
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
       <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>52</v>
@@ -2990,7 +2933,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N18" s="10">
         <v>44109</v>
@@ -2998,23 +2941,23 @@
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
       <c r="Q18" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R18" s="10">
         <v>44134</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T18" s="10">
         <v>44161</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V18" s="6"/>
       <c r="W18" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X18" s="10">
         <v>44207</v>
@@ -3023,26 +2966,23 @@
       <c r="Z18" s="10">
         <v>44235</v>
       </c>
-      <c r="AA18" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA18" s="14"/>
       <c r="AB18" s="14"/>
       <c r="AC18" s="14"/>
       <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E19" s="6">
         <v>32</v>
@@ -3070,19 +3010,19 @@
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N19" s="10">
         <v>44564</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R19" s="10">
         <f>N19+28</f>
@@ -3096,7 +3036,7 @@
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X19" s="10">
         <f>T19+28</f>
@@ -3107,26 +3047,23 @@
         <f>X19+28</f>
         <v>44676</v>
       </c>
-      <c r="AA19" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA19" s="14"/>
       <c r="AB19" s="14"/>
       <c r="AC19" s="14"/>
       <c r="AD19" s="14"/>
-      <c r="AE19" s="14"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" s="6">
         <v>37</v>
@@ -3154,19 +3091,19 @@
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N20" s="10">
         <v>44435</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R20" s="10">
         <f>N20+28</f>
@@ -3179,7 +3116,7 @@
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X20" s="15">
         <v>44519</v>
@@ -3189,26 +3126,23 @@
         <f>X20+28</f>
         <v>44547</v>
       </c>
-      <c r="AA20" s="14" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA20" s="14"/>
       <c r="AB20" s="14"/>
       <c r="AC20" s="14"/>
       <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
         <v>40</v>
@@ -3236,7 +3170,7 @@
       </c>
       <c r="L21" s="19"/>
       <c r="M21" s="18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N21" s="9">
         <v>44316</v>
@@ -3244,13 +3178,13 @@
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R21" s="9">
         <v>44344</v>
       </c>
       <c r="S21" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T21" s="15">
         <v>44372</v>
@@ -3258,7 +3192,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="18"/>
       <c r="W21" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X21" s="9">
         <v>44400</v>
@@ -3267,26 +3201,23 @@
       <c r="Z21" s="9">
         <v>44428</v>
       </c>
-      <c r="AA21" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA21" s="14"/>
       <c r="AB21" s="14"/>
       <c r="AC21" s="14"/>
       <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="6">
         <v>41</v>
@@ -3306,17 +3237,17 @@
       <c r="K22" s="7"/>
       <c r="L22" s="8"/>
       <c r="M22" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N22" s="10">
         <v>44323</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q22" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R22" s="10">
         <v>44351</v>
@@ -3328,7 +3259,7 @@
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X22" s="15">
         <v>44414</v>
@@ -3337,26 +3268,23 @@
       <c r="Z22" s="10">
         <v>44442</v>
       </c>
-      <c r="AA22" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA22" s="14"/>
       <c r="AB22" s="14"/>
       <c r="AC22" s="14"/>
       <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" s="6">
         <v>43</v>
@@ -3376,7 +3304,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N23" s="10">
         <v>44109</v>
@@ -3384,23 +3312,23 @@
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
       <c r="Q23" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R23" s="10">
         <v>44137</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T23" s="10">
         <v>44165</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V23" s="6"/>
       <c r="W23" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X23" s="10">
         <v>44210</v>
@@ -3409,26 +3337,23 @@
       <c r="Z23" s="10">
         <v>44238</v>
       </c>
-      <c r="AA23" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA23" s="14"/>
       <c r="AB23" s="14"/>
       <c r="AC23" s="14"/>
       <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>30</v>
@@ -3448,7 +3373,7 @@
       <c r="K24" s="7"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N24" s="10">
         <v>44109</v>
@@ -3456,23 +3381,23 @@
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
       <c r="Q24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24" s="10">
         <v>44137</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T24" s="10">
         <v>44165</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V24" s="6"/>
       <c r="W24" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X24" s="10">
         <v>44210</v>
@@ -3485,20 +3410,19 @@
       <c r="AB24" s="14"/>
       <c r="AC24" s="14"/>
       <c r="AD24" s="14"/>
-      <c r="AE24" s="14"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E25" s="6">
         <v>25</v>
@@ -3518,7 +3442,7 @@
       <c r="K25" s="7"/>
       <c r="L25" s="8"/>
       <c r="M25" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N25" s="10">
         <v>44111</v>
@@ -3526,23 +3450,23 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
       <c r="Q25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R25" s="10">
         <v>44139</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T25" s="20">
         <v>44168</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V25" s="6"/>
       <c r="W25" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X25" s="10">
         <v>44209</v>
@@ -3551,26 +3475,23 @@
       <c r="Z25" s="10">
         <v>44237</v>
       </c>
-      <c r="AA25" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA25" s="14"/>
       <c r="AB25" s="14"/>
       <c r="AC25" s="14"/>
       <c r="AD25" s="14"/>
-      <c r="AE25" s="14"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>59</v>
@@ -3590,7 +3511,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="21"/>
       <c r="M26" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N26" s="10">
         <v>44320</v>
@@ -3598,7 +3519,7 @@
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R26" s="10">
         <v>44348</v>
@@ -3610,7 +3531,7 @@
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X26" s="15">
         <v>44411</v>
@@ -3619,26 +3540,23 @@
       <c r="Z26" s="10">
         <v>44439</v>
       </c>
-      <c r="AA26" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA26" s="14"/>
       <c r="AB26" s="14"/>
       <c r="AC26" s="14"/>
       <c r="AD26" s="14"/>
-      <c r="AE26" s="14"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="23">
         <v>21</v>
@@ -3658,19 +3576,19 @@
       <c r="K27" s="24"/>
       <c r="L27" s="23"/>
       <c r="M27" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N27" s="25">
         <v>44438</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P27" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R27" s="25">
         <f>N27+28</f>
@@ -3684,7 +3602,7 @@
       <c r="U27" s="29"/>
       <c r="V27" s="29"/>
       <c r="W27" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X27" s="25">
         <f>T27+28</f>
@@ -3699,20 +3617,19 @@
       <c r="AB27" s="30"/>
       <c r="AC27" s="30"/>
       <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" s="6">
         <v>22</v>
@@ -3740,19 +3657,19 @@
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N28" s="10">
         <v>44435</v>
       </c>
       <c r="O28" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R28" s="10">
         <f>N28+28</f>
@@ -3766,7 +3683,7 @@
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X28" s="10">
         <f>T28+28</f>
@@ -3777,26 +3694,23 @@
         <f>X28+28</f>
         <v>44547</v>
       </c>
-      <c r="AA28" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA28" s="14"/>
       <c r="AB28" s="14"/>
       <c r="AC28" s="14"/>
       <c r="AD28" s="14"/>
-      <c r="AE28" s="14"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E29" s="6">
         <v>25</v>
@@ -3816,7 +3730,7 @@
       <c r="K29" s="7"/>
       <c r="L29" s="8"/>
       <c r="M29" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N29" s="10">
         <v>44118</v>
@@ -3824,23 +3738,23 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R29" s="10">
         <v>44146</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T29" s="10">
         <v>44174</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V29" s="6"/>
       <c r="W29" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X29" s="10">
         <v>44210</v>
@@ -3849,26 +3763,23 @@
       <c r="Z29" s="10">
         <v>44243</v>
       </c>
-      <c r="AA29" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA29" s="14"/>
       <c r="AB29" s="14"/>
       <c r="AC29" s="14"/>
       <c r="AD29" s="14"/>
-      <c r="AE29" s="14"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E30" s="6">
         <v>41</v>
@@ -3896,7 +3807,7 @@
       </c>
       <c r="L30" s="31"/>
       <c r="M30" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N30" s="10">
         <v>44441</v>
@@ -3904,7 +3815,7 @@
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R30" s="10">
         <f>N30+28</f>
@@ -3918,7 +3829,7 @@
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X30" s="10">
         <f>T30+28</f>
@@ -3929,26 +3840,23 @@
         <f>X30+28</f>
         <v>44553</v>
       </c>
-      <c r="AA30" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA30" s="14"/>
       <c r="AB30" s="14"/>
       <c r="AC30" s="14"/>
       <c r="AD30" s="14"/>
-      <c r="AE30" s="14"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" s="6">
         <v>57</v>
@@ -3968,7 +3876,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N31" s="10">
         <v>44333</v>
@@ -3976,7 +3884,7 @@
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R31" s="10">
         <v>44361</v>
@@ -3988,7 +3896,7 @@
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X31" s="9">
         <v>44419</v>
@@ -3997,26 +3905,23 @@
       <c r="Z31" s="15">
         <v>44447</v>
       </c>
-      <c r="AA31" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA31" s="14"/>
       <c r="AB31" s="14"/>
       <c r="AC31" s="14"/>
       <c r="AD31" s="14"/>
-      <c r="AE31" s="14"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E32" s="6">
         <v>27</v>
@@ -4044,19 +3949,19 @@
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N32" s="10">
         <v>44435</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q32" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R32" s="10">
         <f>N32+28</f>
@@ -4069,7 +3974,7 @@
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X32" s="10">
         <v>44519</v>
@@ -4079,26 +3984,23 @@
         <f>X32+28</f>
         <v>44547</v>
       </c>
-      <c r="AA32" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA32" s="14"/>
       <c r="AB32" s="14"/>
       <c r="AC32" s="14"/>
       <c r="AD32" s="14"/>
-      <c r="AE32" s="14"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33" s="18">
         <v>23</v>
@@ -4126,7 +4028,7 @@
       </c>
       <c r="L33" s="19"/>
       <c r="M33" s="18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N33" s="9">
         <v>44490</v>
@@ -4134,7 +4036,7 @@
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R33" s="10">
         <f>N33+28</f>
@@ -4148,7 +4050,7 @@
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
       <c r="W33" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X33" s="10">
         <f>T33+28</f>
@@ -4159,26 +4061,23 @@
         <f>X33+28</f>
         <v>44602</v>
       </c>
-      <c r="AA33" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA33" s="14"/>
       <c r="AB33" s="14"/>
       <c r="AC33" s="14"/>
       <c r="AD33" s="14"/>
-      <c r="AE33" s="14"/>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" s="18">
         <v>20</v>
@@ -4206,17 +4105,17 @@
       </c>
       <c r="L34" s="19"/>
       <c r="M34" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N34" s="10">
         <v>44319</v>
       </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q34" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R34" s="10">
         <v>44347</v>
@@ -4228,7 +4127,7 @@
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
       <c r="W34" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X34" s="10">
         <v>44403</v>
@@ -4237,26 +4136,23 @@
       <c r="Z34" s="10">
         <v>44431</v>
       </c>
-      <c r="AA34" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA34" s="14"/>
       <c r="AB34" s="14"/>
       <c r="AC34" s="14"/>
       <c r="AD34" s="14"/>
-      <c r="AE34" s="14"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E35" s="6">
         <v>27</v>
@@ -4284,23 +4180,23 @@
       </c>
       <c r="L35" s="8"/>
       <c r="M35" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N35" s="10">
         <v>44315</v>
       </c>
       <c r="O35" s="10"/>
       <c r="P35" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R35" s="10">
         <v>44343</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T35" s="15">
         <v>44372</v>
@@ -4308,7 +4204,7 @@
       <c r="U35" s="6"/>
       <c r="V35" s="6"/>
       <c r="W35" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X35" s="10">
         <v>44400</v>
@@ -4317,26 +4213,23 @@
       <c r="Z35" s="10">
         <v>44428</v>
       </c>
-      <c r="AA35" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA35" s="14"/>
       <c r="AB35" s="14"/>
       <c r="AC35" s="14"/>
       <c r="AD35" s="14"/>
-      <c r="AE35" s="14"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E36" s="6">
         <v>60</v>
@@ -4364,7 +4257,7 @@
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N36" s="10">
         <v>44553</v>
@@ -4372,7 +4265,7 @@
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
       <c r="Q36" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R36" s="10">
         <f t="shared" ref="R36:R44" si="3">N36+28</f>
@@ -4386,7 +4279,7 @@
       <c r="U36" s="6"/>
       <c r="V36" s="6"/>
       <c r="W36" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X36" s="10">
         <f t="shared" ref="X36:X44" si="5">T36+28</f>
@@ -4397,26 +4290,23 @@
         <f t="shared" ref="Z36:Z44" si="6">X36+28</f>
         <v>44665</v>
       </c>
-      <c r="AA36" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA36" s="14"/>
       <c r="AB36" s="14"/>
       <c r="AC36" s="14"/>
-      <c r="AD36" s="14"/>
-      <c r="AE36"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD36"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" s="6">
         <v>60</v>
@@ -4444,19 +4334,19 @@
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N37" s="9">
         <v>44438</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q37" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R37" s="10">
         <f t="shared" si="3"/>
@@ -4470,7 +4360,7 @@
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
       <c r="W37" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X37" s="10">
         <f t="shared" si="5"/>
@@ -4481,26 +4371,23 @@
         <f t="shared" si="6"/>
         <v>44550</v>
       </c>
-      <c r="AA37" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA37" s="14"/>
       <c r="AB37" s="14"/>
       <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="32"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD37" s="32"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" s="18">
         <v>39</v>
@@ -4528,17 +4415,17 @@
       </c>
       <c r="L38" s="18"/>
       <c r="M38" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N38" s="10">
         <v>44489</v>
       </c>
       <c r="O38" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P38" s="10"/>
       <c r="Q38" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R38" s="10">
         <f t="shared" si="3"/>
@@ -4552,7 +4439,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
       <c r="W38" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X38" s="10">
         <f t="shared" si="5"/>
@@ -4563,26 +4450,23 @@
         <f t="shared" si="6"/>
         <v>44601</v>
       </c>
-      <c r="AA38" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA38" s="14"/>
       <c r="AB38" s="14"/>
       <c r="AC38" s="14"/>
       <c r="AD38" s="14"/>
-      <c r="AE38" s="14"/>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" s="6">
         <v>59</v>
@@ -4610,19 +4494,19 @@
       </c>
       <c r="L39" s="21"/>
       <c r="M39" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="N39" s="10">
         <v>44440</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q39" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R39" s="10">
         <f t="shared" si="3"/>
@@ -4636,7 +4520,7 @@
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X39" s="10">
         <f t="shared" si="5"/>
@@ -4647,26 +4531,23 @@
         <f t="shared" si="6"/>
         <v>44552</v>
       </c>
-      <c r="AA39" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA39" s="14"/>
       <c r="AB39" s="14"/>
       <c r="AC39" s="14"/>
       <c r="AD39" s="14"/>
-      <c r="AE39" s="14"/>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" s="27">
         <v>40</v>
@@ -4686,19 +4567,19 @@
       <c r="K40" s="24"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N40" s="25">
         <v>44439</v>
       </c>
       <c r="O40" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P40" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q40" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R40" s="25">
         <f t="shared" si="3"/>
@@ -4712,7 +4593,7 @@
       <c r="U40" s="27"/>
       <c r="V40" s="27"/>
       <c r="W40" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X40" s="25">
         <f t="shared" si="5"/>
@@ -4727,20 +4608,19 @@
       <c r="AB40" s="30"/>
       <c r="AC40" s="30"/>
       <c r="AD40" s="30"/>
-      <c r="AE40" s="30"/>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" s="18">
         <v>28</v>
@@ -4768,7 +4648,7 @@
       </c>
       <c r="L41" s="19"/>
       <c r="M41" s="18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N41" s="10">
         <v>44489</v>
@@ -4776,7 +4656,7 @@
       <c r="O41" s="9"/>
       <c r="P41" s="10"/>
       <c r="Q41" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R41" s="10">
         <f t="shared" si="3"/>
@@ -4790,7 +4670,7 @@
       <c r="U41" s="18"/>
       <c r="V41" s="18"/>
       <c r="W41" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X41" s="10">
         <f t="shared" si="5"/>
@@ -4801,26 +4681,23 @@
         <f t="shared" si="6"/>
         <v>44601</v>
       </c>
-      <c r="AA41" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA41" s="14"/>
       <c r="AB41" s="14"/>
       <c r="AC41" s="14"/>
       <c r="AD41" s="14"/>
-      <c r="AE41" s="14"/>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E42" s="27">
         <v>26</v>
@@ -4840,17 +4717,17 @@
       <c r="K42" s="24"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N42" s="25">
         <v>44515</v>
       </c>
       <c r="O42" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P42" s="25"/>
       <c r="Q42" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R42" s="25">
         <f t="shared" si="3"/>
@@ -4876,21 +4753,20 @@
       <c r="AA42" s="30"/>
       <c r="AB42" s="30"/>
       <c r="AC42" s="30"/>
-      <c r="AD42" s="30"/>
-      <c r="AE42" s="14"/>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD42" s="14"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" s="18">
         <v>41</v>
@@ -4918,19 +4794,19 @@
       </c>
       <c r="L43" s="8"/>
       <c r="M43" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N43" s="10">
         <v>44066</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q43" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R43" s="10">
         <f t="shared" si="3"/>
@@ -4944,7 +4820,7 @@
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="W43" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X43" s="10">
         <f t="shared" si="5"/>
@@ -4955,26 +4831,23 @@
         <f t="shared" si="6"/>
         <v>44178</v>
       </c>
-      <c r="AA43" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA43" s="14"/>
       <c r="AB43" s="14"/>
       <c r="AC43" s="14"/>
       <c r="AD43" s="14"/>
-      <c r="AE43" s="14"/>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E44" s="18">
         <v>33</v>
@@ -5002,19 +4875,19 @@
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N44" s="10">
         <v>44439</v>
       </c>
       <c r="O44" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q44" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R44" s="10">
         <f t="shared" si="3"/>
@@ -5028,7 +4901,7 @@
       <c r="U44" s="18"/>
       <c r="V44" s="18"/>
       <c r="W44" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X44" s="10">
         <f t="shared" si="5"/>
@@ -5039,26 +4912,23 @@
         <f t="shared" si="6"/>
         <v>44551</v>
       </c>
-      <c r="AA44" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA44" s="14"/>
       <c r="AB44" s="14"/>
       <c r="AC44" s="14"/>
-      <c r="AD44" s="14"/>
-      <c r="AE44" s="18"/>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD44" s="18"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E45" s="18">
         <v>34</v>
@@ -5078,7 +4948,7 @@
       <c r="K45" s="7"/>
       <c r="L45" s="18"/>
       <c r="M45" s="18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N45" s="10">
         <v>44123</v>
@@ -5086,23 +4956,23 @@
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
       <c r="Q45" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R45" s="10">
         <v>44151</v>
       </c>
       <c r="S45" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T45" s="10">
         <v>44179</v>
       </c>
       <c r="U45" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V45" s="18"/>
       <c r="W45" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X45" s="9">
         <v>44215</v>
@@ -5111,26 +4981,23 @@
       <c r="Z45" s="9">
         <v>44243</v>
       </c>
-      <c r="AA45" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA45" s="14"/>
       <c r="AB45" s="14"/>
       <c r="AC45" s="14"/>
       <c r="AD45" s="14"/>
-      <c r="AE45" s="14"/>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E46" s="6">
         <v>23</v>
@@ -5158,17 +5025,17 @@
       </c>
       <c r="L46" s="21"/>
       <c r="M46" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N46" s="10">
         <v>44319</v>
       </c>
       <c r="O46" s="10"/>
       <c r="P46" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R46" s="10">
         <v>44347</v>
@@ -5180,7 +5047,7 @@
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X46" s="10">
         <v>44441</v>
@@ -5190,26 +5057,23 @@
         <f t="shared" ref="Z46:Z61" si="7">X46+28</f>
         <v>44469</v>
       </c>
-      <c r="AA46" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA46" s="14"/>
       <c r="AB46" s="14"/>
       <c r="AC46" s="14"/>
-      <c r="AD46" s="14"/>
-      <c r="AE46" s="7"/>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD46" s="7"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E47" s="6">
         <v>54</v>
@@ -5237,24 +5101,24 @@
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N47" s="10">
         <v>44460</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R47" s="10">
         <f>N47+28</f>
         <v>44488</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="T47" s="10">
         <f>R47+28</f>
@@ -5263,7 +5127,7 @@
       <c r="U47" s="6"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X47" s="10">
         <f t="shared" ref="X47:X61" si="8">T47+28</f>
@@ -5274,26 +5138,23 @@
         <f t="shared" si="7"/>
         <v>44572</v>
       </c>
-      <c r="AA47" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB47" s="7"/>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="14"/>
       <c r="AC47" s="14"/>
-      <c r="AD47" s="14"/>
-      <c r="AE47" s="7"/>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD47" s="7"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E48" s="18">
         <v>57</v>
@@ -5321,19 +5182,19 @@
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N48" s="9">
         <v>44440</v>
       </c>
       <c r="O48" s="33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P48" s="33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q48" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R48" s="15">
         <v>44469</v>
@@ -5345,7 +5206,7 @@
       <c r="U48" s="18"/>
       <c r="V48" s="18"/>
       <c r="W48" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X48" s="10">
         <f t="shared" si="8"/>
@@ -5356,26 +5217,23 @@
         <f t="shared" si="7"/>
         <v>44552</v>
       </c>
-      <c r="AA48" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA48" s="14"/>
       <c r="AB48" s="14"/>
       <c r="AC48" s="14"/>
       <c r="AD48" s="14"/>
-      <c r="AE48" s="14"/>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E49" s="6">
         <v>28</v>
@@ -5403,17 +5261,17 @@
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N49" s="10">
         <v>44439</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q49" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R49" s="10">
         <f t="shared" ref="R49:R61" si="9">N49+28</f>
@@ -5427,7 +5285,7 @@
       <c r="U49" s="6"/>
       <c r="V49" s="6"/>
       <c r="W49" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X49" s="10">
         <f t="shared" si="8"/>
@@ -5438,26 +5296,23 @@
         <f t="shared" si="7"/>
         <v>44551</v>
       </c>
-      <c r="AA49" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA49" s="14"/>
       <c r="AB49" s="14"/>
       <c r="AC49" s="14"/>
       <c r="AD49" s="14"/>
-      <c r="AE49" s="14"/>
-    </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E50" s="6">
         <v>25</v>
@@ -5485,19 +5340,19 @@
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N50" s="9">
         <v>44439</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q50" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R50" s="10">
         <f t="shared" si="9"/>
@@ -5511,7 +5366,7 @@
       <c r="U50" s="6"/>
       <c r="V50" s="6"/>
       <c r="W50" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X50" s="10">
         <f t="shared" si="8"/>
@@ -5522,26 +5377,23 @@
         <f t="shared" si="7"/>
         <v>44551</v>
       </c>
-      <c r="AA50" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA50" s="14"/>
       <c r="AB50" s="14"/>
       <c r="AC50" s="14"/>
       <c r="AD50" s="14"/>
-      <c r="AE50" s="14"/>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="6">
         <v>43</v>
@@ -5569,7 +5421,7 @@
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N51" s="10">
         <v>44460</v>
@@ -5577,7 +5429,7 @@
       <c r="O51" s="10"/>
       <c r="P51" s="10"/>
       <c r="Q51" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R51" s="10">
         <f t="shared" si="9"/>
@@ -5591,7 +5443,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X51" s="10">
         <f t="shared" si="8"/>
@@ -5602,26 +5454,23 @@
         <f t="shared" si="7"/>
         <v>44572</v>
       </c>
-      <c r="AA51" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB51" s="7"/>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="14"/>
       <c r="AC51" s="14"/>
-      <c r="AD51" s="14"/>
-      <c r="AE51" s="7"/>
-    </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD51" s="7"/>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E52" s="6">
         <v>41</v>
@@ -5649,7 +5498,7 @@
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N52" s="10">
         <v>44460</v>
@@ -5657,7 +5506,7 @@
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
       <c r="Q52" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R52" s="10">
         <f t="shared" si="9"/>
@@ -5671,7 +5520,7 @@
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X52" s="10">
         <f t="shared" si="8"/>
@@ -5682,26 +5531,23 @@
         <f t="shared" si="7"/>
         <v>44572</v>
       </c>
-      <c r="AA52" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB52" s="7"/>
+      <c r="AA52" s="7"/>
+      <c r="AB52" s="14"/>
       <c r="AC52" s="14"/>
-      <c r="AD52" s="14"/>
-      <c r="AE52" s="7"/>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD52" s="7"/>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E53" s="6">
         <v>27</v>
@@ -5729,7 +5575,7 @@
       </c>
       <c r="L53" s="31"/>
       <c r="M53" s="18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N53" s="10">
         <v>44439</v>
@@ -5737,14 +5583,14 @@
       <c r="O53" s="10"/>
       <c r="P53" s="10"/>
       <c r="Q53" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R53" s="10">
         <f t="shared" si="9"/>
         <v>44467</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="T53" s="10">
         <f t="shared" si="10"/>
@@ -5753,7 +5599,7 @@
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X53" s="10">
         <f t="shared" si="8"/>
@@ -5764,26 +5610,23 @@
         <f t="shared" si="7"/>
         <v>44551</v>
       </c>
-      <c r="AA53" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB53" s="13"/>
+      <c r="AA53" s="13"/>
+      <c r="AB53" s="14"/>
       <c r="AC53" s="14"/>
       <c r="AD53" s="14"/>
-      <c r="AE53" s="14"/>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E54" s="18">
         <v>21</v>
@@ -5811,19 +5654,19 @@
       </c>
       <c r="L54" s="31"/>
       <c r="M54" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N54" s="10">
         <v>44059</v>
       </c>
       <c r="O54" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q54" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R54" s="10">
         <f t="shared" si="9"/>
@@ -5837,7 +5680,7 @@
       <c r="U54" s="6"/>
       <c r="V54" s="6"/>
       <c r="W54" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X54" s="10">
         <f t="shared" si="8"/>
@@ -5848,26 +5691,23 @@
         <f t="shared" si="7"/>
         <v>44171</v>
       </c>
-      <c r="AA54" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA54" s="14"/>
       <c r="AB54" s="14"/>
       <c r="AC54" s="14"/>
       <c r="AD54" s="14"/>
-      <c r="AE54" s="14"/>
-    </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E55" s="6">
         <v>42</v>
@@ -5895,7 +5735,7 @@
       </c>
       <c r="L55" s="17"/>
       <c r="M55" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N55" s="10">
         <v>44462</v>
@@ -5903,7 +5743,7 @@
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R55" s="10">
         <f t="shared" si="9"/>
@@ -5917,7 +5757,7 @@
       <c r="U55" s="6"/>
       <c r="V55" s="6"/>
       <c r="W55" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X55" s="10">
         <f t="shared" si="8"/>
@@ -5928,26 +5768,23 @@
         <f t="shared" si="7"/>
         <v>44574</v>
       </c>
-      <c r="AA55" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA55" s="14"/>
       <c r="AB55" s="14"/>
       <c r="AC55" s="14"/>
       <c r="AD55" s="14"/>
-      <c r="AE55" s="14"/>
-    </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E56" s="6">
         <v>52</v>
@@ -5975,7 +5812,7 @@
       </c>
       <c r="L56" s="31"/>
       <c r="M56" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N56" s="10">
         <v>44543</v>
@@ -5983,7 +5820,7 @@
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
       <c r="Q56" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R56" s="10">
         <f t="shared" si="9"/>
@@ -5997,7 +5834,7 @@
       <c r="U56" s="6"/>
       <c r="V56" s="6"/>
       <c r="W56" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X56" s="10">
         <f t="shared" si="8"/>
@@ -6012,20 +5849,19 @@
       <c r="AB56" s="7"/>
       <c r="AC56" s="7"/>
       <c r="AD56" s="7"/>
-      <c r="AE56" s="7"/>
-    </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57" s="6">
         <v>57</v>
@@ -6053,7 +5889,7 @@
       </c>
       <c r="L57" s="31"/>
       <c r="M57" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N57" s="10">
         <v>44496</v>
@@ -6061,7 +5897,7 @@
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
       <c r="Q57" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R57" s="10">
         <f t="shared" si="9"/>
@@ -6075,7 +5911,7 @@
       <c r="U57" s="6"/>
       <c r="V57" s="6"/>
       <c r="W57" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X57" s="10">
         <f t="shared" si="8"/>
@@ -6086,26 +5922,23 @@
         <f t="shared" si="7"/>
         <v>44608</v>
       </c>
-      <c r="AA57" s="14" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA57" s="14"/>
       <c r="AB57" s="14"/>
       <c r="AC57" s="14"/>
       <c r="AD57" s="14"/>
-      <c r="AE57" s="14"/>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E58" s="6">
         <v>38</v>
@@ -6133,19 +5966,19 @@
       </c>
       <c r="L58" s="31"/>
       <c r="M58" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N58" s="10">
         <v>44059</v>
       </c>
       <c r="O58" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q58" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R58" s="10">
         <f t="shared" si="9"/>
@@ -6159,7 +5992,7 @@
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X58" s="10">
         <f t="shared" si="8"/>
@@ -6170,26 +6003,23 @@
         <f t="shared" si="7"/>
         <v>44171</v>
       </c>
-      <c r="AA58" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA58" s="14"/>
       <c r="AB58" s="14"/>
       <c r="AC58" s="14"/>
       <c r="AD58" s="14"/>
-      <c r="AE58" s="14"/>
-    </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E59" s="6">
         <v>43</v>
@@ -6217,19 +6047,19 @@
       </c>
       <c r="L59" s="31"/>
       <c r="M59" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N59" s="10">
         <v>44059</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q59" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R59" s="10">
         <f t="shared" si="9"/>
@@ -6243,7 +6073,7 @@
       <c r="U59" s="6"/>
       <c r="V59" s="6"/>
       <c r="W59" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X59" s="10">
         <f t="shared" si="8"/>
@@ -6254,26 +6084,23 @@
         <f t="shared" si="7"/>
         <v>44171</v>
       </c>
-      <c r="AA59" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA59" s="14"/>
       <c r="AB59" s="14"/>
       <c r="AC59" s="14"/>
       <c r="AD59" s="14"/>
-      <c r="AE59" s="14"/>
-    </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E60" s="6">
         <v>56</v>
@@ -6301,7 +6128,7 @@
       </c>
       <c r="L60" s="31"/>
       <c r="M60" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N60" s="10">
         <v>44459</v>
@@ -6309,7 +6136,7 @@
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
       <c r="Q60" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R60" s="10">
         <f t="shared" si="9"/>
@@ -6323,7 +6150,7 @@
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
       <c r="W60" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X60" s="10">
         <f t="shared" si="8"/>
@@ -6334,26 +6161,23 @@
         <f t="shared" si="7"/>
         <v>44571</v>
       </c>
-      <c r="AA60" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA60" s="14"/>
       <c r="AB60" s="14"/>
       <c r="AC60" s="14"/>
-      <c r="AD60" s="14"/>
-      <c r="AE60" s="7"/>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD60" s="7"/>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E61" s="6">
         <v>57</v>
@@ -6381,19 +6205,19 @@
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N61" s="10">
         <v>44440</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q61" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R61" s="10">
         <f t="shared" si="9"/>
@@ -6407,7 +6231,7 @@
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
       <c r="W61" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X61" s="10">
         <f t="shared" si="8"/>
@@ -6418,26 +6242,23 @@
         <f t="shared" si="7"/>
         <v>44552</v>
       </c>
-      <c r="AA61" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA61" s="14"/>
       <c r="AB61" s="14"/>
       <c r="AC61" s="14"/>
       <c r="AD61" s="14"/>
-      <c r="AE61" s="14"/>
-    </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E62" s="23">
         <v>29</v>
@@ -6467,17 +6288,17 @@
         <v>44152</v>
       </c>
       <c r="S62" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T62" s="28">
         <v>44180</v>
       </c>
       <c r="U62" s="23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="V62" s="23"/>
       <c r="W62" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X62" s="26"/>
       <c r="Y62" s="23"/>
@@ -6486,20 +6307,19 @@
       <c r="AB62" s="24"/>
       <c r="AC62" s="24"/>
       <c r="AD62" s="24"/>
-      <c r="AE62" s="24"/>
-    </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E63" s="6">
         <v>55</v>
@@ -6527,19 +6347,19 @@
       </c>
       <c r="L63" s="6"/>
       <c r="M63" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N63" s="10">
         <v>44440</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q63" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R63" s="10">
         <f>N63+28</f>
@@ -6553,7 +6373,7 @@
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X63" s="15">
         <v>44215</v>
@@ -6563,26 +6383,23 @@
         <f>X63+28</f>
         <v>44243</v>
       </c>
-      <c r="AA63" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA63" s="14"/>
       <c r="AB63" s="14"/>
       <c r="AC63" s="14"/>
       <c r="AD63" s="14"/>
-      <c r="AE63" s="14"/>
-    </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E64" s="6">
         <v>20</v>
@@ -6602,7 +6419,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N64" s="10">
         <v>44124</v>
@@ -6610,23 +6427,23 @@
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
       <c r="Q64" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R64" s="10">
         <v>44152</v>
       </c>
       <c r="S64" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T64" s="10">
         <v>44180</v>
       </c>
       <c r="U64" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V64" s="6"/>
       <c r="W64" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X64" s="10">
         <v>44208</v>
@@ -6635,26 +6452,23 @@
       <c r="Z64" s="10">
         <v>44239</v>
       </c>
-      <c r="AA64" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA64" s="14"/>
       <c r="AB64" s="14"/>
       <c r="AC64" s="14"/>
       <c r="AD64" s="14"/>
-      <c r="AE64" s="14"/>
-    </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E65" s="6">
         <v>52</v>
@@ -6674,7 +6488,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N65" s="10">
         <v>44124</v>
@@ -6682,23 +6496,23 @@
       <c r="O65" s="10"/>
       <c r="P65" s="10"/>
       <c r="Q65" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R65" s="10">
         <v>44152</v>
       </c>
       <c r="S65" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T65" s="10">
         <v>44180</v>
       </c>
       <c r="U65" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V65" s="6"/>
       <c r="W65" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X65" s="10">
         <v>44208</v>
@@ -6707,26 +6521,23 @@
       <c r="Z65" s="10">
         <v>44239</v>
       </c>
-      <c r="AA65" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA65" s="14"/>
       <c r="AB65" s="14"/>
       <c r="AC65" s="14"/>
       <c r="AD65" s="14"/>
-      <c r="AE65" s="14"/>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E66" s="6">
         <v>53</v>
@@ -6754,7 +6565,7 @@
       </c>
       <c r="L66" s="6"/>
       <c r="M66" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N66" s="10">
         <v>44490</v>
@@ -6762,7 +6573,7 @@
       <c r="O66" s="10"/>
       <c r="P66" s="10"/>
       <c r="Q66" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R66" s="10">
         <f>N66+28</f>
@@ -6776,7 +6587,7 @@
       <c r="U66" s="6"/>
       <c r="V66" s="6"/>
       <c r="W66" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X66" s="10">
         <f>T66+28</f>
@@ -6791,20 +6602,19 @@
       <c r="AB66" s="14"/>
       <c r="AC66" s="14"/>
       <c r="AD66" s="14"/>
-      <c r="AE66" s="14"/>
-    </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E67" s="6">
         <v>33</v>
@@ -6832,19 +6642,19 @@
       </c>
       <c r="L67" s="6"/>
       <c r="M67" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N67" s="10">
         <v>44059</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q67" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R67" s="10">
         <f>N67+28</f>
@@ -6858,7 +6668,7 @@
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
       <c r="W67" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X67" s="10">
         <f>T67+28</f>
@@ -6869,26 +6679,23 @@
         <f>X67+28</f>
         <v>44171</v>
       </c>
-      <c r="AA67" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA67" s="14"/>
       <c r="AB67" s="14"/>
       <c r="AC67" s="14"/>
       <c r="AD67" s="14"/>
-      <c r="AE67" s="14"/>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E68" s="6">
         <v>30</v>
@@ -6916,7 +6723,7 @@
       </c>
       <c r="L68" s="6"/>
       <c r="M68" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N68" s="10">
         <v>44490</v>
@@ -6924,7 +6731,7 @@
       <c r="O68" s="10"/>
       <c r="P68" s="10"/>
       <c r="Q68" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R68" s="10">
         <f>N68+28</f>
@@ -6938,31 +6745,28 @@
       <c r="U68" s="6"/>
       <c r="V68" s="6"/>
       <c r="W68" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X68" s="16"/>
       <c r="Y68" s="6"/>
       <c r="Z68" s="16"/>
-      <c r="AA68" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB68" s="18"/>
+      <c r="AA68" s="18"/>
+      <c r="AB68" s="14"/>
       <c r="AC68" s="14"/>
       <c r="AD68" s="14"/>
-      <c r="AE68" s="14"/>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69" s="6">
         <v>33</v>
@@ -6990,17 +6794,17 @@
       </c>
       <c r="L69" s="6"/>
       <c r="M69" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N69" s="10">
         <v>44251</v>
       </c>
       <c r="O69" s="10"/>
       <c r="P69" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R69" s="10">
         <v>44279</v>
@@ -7012,7 +6816,7 @@
       <c r="U69" s="6"/>
       <c r="V69" s="6"/>
       <c r="W69" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X69" s="10">
         <v>44336</v>
@@ -7021,26 +6825,23 @@
       <c r="Z69" s="10">
         <v>44364</v>
       </c>
-      <c r="AA69" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA69" s="14"/>
       <c r="AB69" s="14"/>
       <c r="AC69" s="14"/>
       <c r="AD69" s="14"/>
-      <c r="AE69" s="14"/>
-    </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E70" s="6">
         <v>58</v>
@@ -7068,7 +6869,7 @@
       </c>
       <c r="L70" s="6"/>
       <c r="M70" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N70" s="10">
         <v>44488</v>
@@ -7076,7 +6877,7 @@
       <c r="O70" s="16"/>
       <c r="P70" s="16"/>
       <c r="Q70" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R70" s="10">
         <f>N70+28</f>
@@ -7090,7 +6891,7 @@
       <c r="U70" s="6"/>
       <c r="V70" s="6"/>
       <c r="W70" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X70" s="10">
         <f>T70+28</f>
@@ -7101,26 +6902,23 @@
         <f>X70+28</f>
         <v>44600</v>
       </c>
-      <c r="AA70" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA70" s="14"/>
       <c r="AB70" s="14"/>
       <c r="AC70" s="14"/>
-      <c r="AD70" s="14"/>
-      <c r="AE70" s="18"/>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD70" s="18"/>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E71" s="6">
         <v>27</v>
@@ -7148,19 +6946,19 @@
       </c>
       <c r="L71" s="6"/>
       <c r="M71" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N71" s="10">
         <v>44433</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q71" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R71" s="10">
         <f>N71+28</f>
@@ -7174,7 +6972,7 @@
       <c r="U71" s="6"/>
       <c r="V71" s="6"/>
       <c r="W71" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X71" s="15">
         <v>44523</v>
@@ -7184,26 +6982,23 @@
         <f>X71+28</f>
         <v>44551</v>
       </c>
-      <c r="AA71" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB71" s="18"/>
+      <c r="AA71" s="18"/>
+      <c r="AB71" s="14"/>
       <c r="AC71" s="14"/>
-      <c r="AD71" s="14"/>
-      <c r="AE71" s="18"/>
-    </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD71" s="18"/>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" s="6">
         <v>32</v>
@@ -7227,17 +7022,17 @@
       </c>
       <c r="L72" s="6"/>
       <c r="M72" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N72" s="10">
         <v>44270</v>
       </c>
       <c r="O72" s="10"/>
       <c r="P72" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R72" s="10">
         <v>44298</v>
@@ -7249,7 +7044,7 @@
       <c r="U72" s="6"/>
       <c r="V72" s="6"/>
       <c r="W72" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X72" s="10">
         <v>44354</v>
@@ -7258,26 +7053,23 @@
       <c r="Z72" s="10">
         <v>44382</v>
       </c>
-      <c r="AA72" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA72" s="14"/>
       <c r="AB72" s="14"/>
       <c r="AC72" s="14"/>
       <c r="AD72" s="14"/>
-      <c r="AE72" s="14"/>
-    </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E73" s="6">
         <v>60</v>
@@ -7305,19 +7097,19 @@
       </c>
       <c r="L73" s="6"/>
       <c r="M73" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N73" s="10">
         <v>44410</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P73" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R73" s="10">
         <f t="shared" ref="R73:R101" si="14">N73+28</f>
@@ -7331,7 +7123,7 @@
       <c r="U73" s="6"/>
       <c r="V73" s="6"/>
       <c r="W73" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X73" s="10">
         <f t="shared" ref="X73:X101" si="16">T73+28</f>
@@ -7342,26 +7134,23 @@
         <f t="shared" ref="Z73:Z101" si="17">X73+28</f>
         <v>44522</v>
       </c>
-      <c r="AA73" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB73" s="18"/>
+      <c r="AA73" s="18"/>
+      <c r="AB73" s="14"/>
       <c r="AC73" s="14"/>
-      <c r="AD73" s="14"/>
-      <c r="AE73" s="18"/>
-    </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD73" s="18"/>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E74" s="6">
         <v>42</v>
@@ -7389,7 +7178,7 @@
       </c>
       <c r="L74" s="6"/>
       <c r="M74" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N74" s="10">
         <v>44488</v>
@@ -7397,7 +7186,7 @@
       <c r="O74" s="16"/>
       <c r="P74" s="16"/>
       <c r="Q74" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R74" s="10">
         <f t="shared" si="14"/>
@@ -7411,7 +7200,7 @@
       <c r="U74" s="6"/>
       <c r="V74" s="6"/>
       <c r="W74" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X74" s="10">
         <f t="shared" si="16"/>
@@ -7422,26 +7211,23 @@
         <f t="shared" si="17"/>
         <v>44600</v>
       </c>
-      <c r="AA74" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB74" s="18"/>
+      <c r="AA74" s="18"/>
+      <c r="AB74" s="14"/>
       <c r="AC74" s="14"/>
-      <c r="AD74" s="14"/>
-      <c r="AE74" s="18"/>
-    </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD74" s="18"/>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E75" s="6">
         <v>21</v>
@@ -7469,7 +7255,7 @@
       </c>
       <c r="L75" s="6"/>
       <c r="M75" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N75" s="10">
         <v>44496</v>
@@ -7477,7 +7263,7 @@
       <c r="O75" s="6"/>
       <c r="P75" s="16"/>
       <c r="Q75" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R75" s="10">
         <f t="shared" si="14"/>
@@ -7491,7 +7277,7 @@
       <c r="U75" s="6"/>
       <c r="V75" s="6"/>
       <c r="W75" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X75" s="10">
         <f t="shared" si="16"/>
@@ -7502,26 +7288,23 @@
         <f t="shared" si="17"/>
         <v>44608</v>
       </c>
-      <c r="AA75" s="18" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA75" s="18"/>
       <c r="AB75" s="18"/>
       <c r="AC75" s="18"/>
       <c r="AD75" s="18"/>
-      <c r="AE75" s="18"/>
-    </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E76" s="6">
         <v>31</v>
@@ -7555,7 +7338,7 @@
       <c r="O76" s="16"/>
       <c r="P76" s="16"/>
       <c r="Q76" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R76" s="10">
         <f t="shared" si="14"/>
@@ -7569,7 +7352,7 @@
       <c r="U76" s="6"/>
       <c r="V76" s="6"/>
       <c r="W76" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X76" s="10">
         <f t="shared" si="16"/>
@@ -7580,26 +7363,23 @@
         <f t="shared" si="17"/>
         <v>44676</v>
       </c>
-      <c r="AA76" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB76" s="6"/>
+      <c r="AA76" s="6"/>
+      <c r="AB76" s="14"/>
       <c r="AC76" s="14"/>
-      <c r="AD76" s="14"/>
-      <c r="AE76" s="18"/>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD76" s="18"/>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E77" s="23">
         <v>54</v>
@@ -7619,7 +7399,7 @@
       <c r="K77" s="24"/>
       <c r="L77" s="23"/>
       <c r="M77" s="23" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N77" s="25">
         <v>44461</v>
@@ -7627,7 +7407,7 @@
       <c r="O77" s="26"/>
       <c r="P77" s="26"/>
       <c r="Q77" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R77" s="25">
         <f t="shared" si="14"/>
@@ -7641,7 +7421,7 @@
       <c r="U77" s="23"/>
       <c r="V77" s="23"/>
       <c r="W77" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X77" s="25">
         <f t="shared" si="16"/>
@@ -7656,20 +7436,19 @@
       <c r="AB77" s="23"/>
       <c r="AC77" s="23"/>
       <c r="AD77" s="23"/>
-      <c r="AE77" s="23"/>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E78" s="6">
         <v>57</v>
@@ -7697,7 +7476,7 @@
       </c>
       <c r="L78" s="6"/>
       <c r="M78" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="N78" s="10">
         <v>44494</v>
@@ -7705,7 +7484,7 @@
       <c r="O78" s="16"/>
       <c r="P78" s="16"/>
       <c r="Q78" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R78" s="10">
         <f t="shared" si="14"/>
@@ -7719,7 +7498,7 @@
       <c r="U78" s="6"/>
       <c r="V78" s="6"/>
       <c r="W78" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X78" s="10">
         <f t="shared" si="16"/>
@@ -7730,26 +7509,23 @@
         <f t="shared" si="17"/>
         <v>44606</v>
       </c>
-      <c r="AA78" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB78" s="18"/>
+      <c r="AA78" s="18"/>
+      <c r="AB78" s="14"/>
       <c r="AC78" s="14"/>
-      <c r="AD78" s="14"/>
-      <c r="AE78" s="18"/>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD78" s="18"/>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E79" s="6">
         <v>61</v>
@@ -7777,7 +7553,7 @@
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N79" s="10">
         <v>44468</v>
@@ -7785,7 +7561,7 @@
       <c r="O79" s="16"/>
       <c r="P79" s="16"/>
       <c r="Q79" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R79" s="10">
         <f t="shared" si="14"/>
@@ -7799,7 +7575,7 @@
       <c r="U79" s="6"/>
       <c r="V79" s="6"/>
       <c r="W79" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X79" s="10">
         <f t="shared" si="16"/>
@@ -7810,26 +7586,23 @@
         <f t="shared" si="17"/>
         <v>44580</v>
       </c>
-      <c r="AA79" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB79" s="18"/>
+      <c r="AA79" s="18"/>
+      <c r="AB79" s="14"/>
       <c r="AC79" s="14"/>
-      <c r="AD79" s="14"/>
-      <c r="AE79" s="18"/>
-    </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD79" s="18"/>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E80" s="6">
         <v>23</v>
@@ -7857,7 +7630,7 @@
       </c>
       <c r="L80" s="6"/>
       <c r="M80" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N80" s="10">
         <v>44461</v>
@@ -7865,7 +7638,7 @@
       <c r="O80" s="16"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R80" s="10">
         <f t="shared" si="14"/>
@@ -7879,7 +7652,7 @@
       <c r="U80" s="6"/>
       <c r="V80" s="6"/>
       <c r="W80" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X80" s="10">
         <f t="shared" si="16"/>
@@ -7890,26 +7663,23 @@
         <f t="shared" si="17"/>
         <v>44573</v>
       </c>
-      <c r="AA80" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB80" s="18"/>
+      <c r="AA80" s="18"/>
+      <c r="AB80" s="14"/>
       <c r="AC80" s="14"/>
-      <c r="AD80" s="14"/>
-      <c r="AE80" s="6"/>
-    </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD80" s="6"/>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E81" s="6">
         <v>31</v>
@@ -7937,7 +7707,7 @@
       </c>
       <c r="L81" s="6"/>
       <c r="M81" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N81" s="10">
         <v>44490</v>
@@ -7945,7 +7715,7 @@
       <c r="O81" s="16"/>
       <c r="P81" s="16"/>
       <c r="Q81" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R81" s="10">
         <f t="shared" si="14"/>
@@ -7959,7 +7729,7 @@
       <c r="U81" s="6"/>
       <c r="V81" s="6"/>
       <c r="W81" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X81" s="10">
         <f t="shared" si="16"/>
@@ -7969,26 +7739,23 @@
       <c r="Z81" s="10">
         <v>44603</v>
       </c>
-      <c r="AA81" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB81" s="18"/>
+      <c r="AA81" s="18"/>
+      <c r="AB81" s="14"/>
       <c r="AC81" s="14"/>
-      <c r="AD81" s="14"/>
-      <c r="AE81" s="18"/>
-    </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD81" s="18"/>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E82" s="6">
         <v>52</v>
@@ -8016,7 +7783,7 @@
       </c>
       <c r="L82" s="6"/>
       <c r="M82" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="N82" s="10">
         <v>44461</v>
@@ -8024,7 +7791,7 @@
       <c r="O82" s="16"/>
       <c r="P82" s="16"/>
       <c r="Q82" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R82" s="10">
         <f t="shared" si="14"/>
@@ -8038,7 +7805,7 @@
       <c r="U82" s="6"/>
       <c r="V82" s="6"/>
       <c r="W82" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X82" s="10">
         <f t="shared" si="16"/>
@@ -8049,26 +7816,23 @@
         <f t="shared" si="17"/>
         <v>44573</v>
       </c>
-      <c r="AA82" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB82" s="18"/>
+      <c r="AA82" s="18"/>
+      <c r="AB82" s="14"/>
       <c r="AC82" s="14"/>
-      <c r="AD82" s="14"/>
-      <c r="AE82" s="6"/>
-    </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD82" s="6"/>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" s="6">
         <v>40</v>
@@ -8096,7 +7860,7 @@
       </c>
       <c r="L83" s="6"/>
       <c r="M83" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N83" s="10">
         <v>44490</v>
@@ -8104,7 +7868,7 @@
       <c r="O83" s="16"/>
       <c r="P83" s="16"/>
       <c r="Q83" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R83" s="10">
         <f t="shared" si="14"/>
@@ -8118,7 +7882,7 @@
       <c r="U83" s="6"/>
       <c r="V83" s="6"/>
       <c r="W83" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X83" s="10">
         <f t="shared" si="16"/>
@@ -8129,26 +7893,23 @@
         <f t="shared" si="17"/>
         <v>44602</v>
       </c>
-      <c r="AA83" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB83" s="6"/>
+      <c r="AA83" s="6"/>
+      <c r="AB83" s="14"/>
       <c r="AC83" s="14"/>
-      <c r="AD83" s="14"/>
-      <c r="AE83" s="18"/>
-    </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD83" s="18"/>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E84" s="6">
         <v>50</v>
@@ -8176,7 +7937,7 @@
       </c>
       <c r="L84" s="6"/>
       <c r="M84" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N84" s="10">
         <v>44487</v>
@@ -8184,7 +7945,7 @@
       <c r="O84" s="16"/>
       <c r="P84" s="16"/>
       <c r="Q84" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R84" s="10">
         <f t="shared" si="14"/>
@@ -8198,7 +7959,7 @@
       <c r="U84" s="6"/>
       <c r="V84" s="6"/>
       <c r="W84" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X84" s="10">
         <f t="shared" si="16"/>
@@ -8209,26 +7970,23 @@
         <f t="shared" si="17"/>
         <v>44599</v>
       </c>
-      <c r="AA84" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB84" s="18"/>
+      <c r="AA84" s="18"/>
+      <c r="AB84" s="14"/>
       <c r="AC84" s="14"/>
-      <c r="AD84" s="14"/>
-      <c r="AE84" s="18"/>
-    </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD84" s="18"/>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E85" s="6">
         <v>53</v>
@@ -8256,7 +8014,7 @@
       </c>
       <c r="L85" s="6"/>
       <c r="M85" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N85" s="10">
         <v>44459</v>
@@ -8264,7 +8022,7 @@
       <c r="O85" s="16"/>
       <c r="P85" s="16"/>
       <c r="Q85" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R85" s="10">
         <f t="shared" si="14"/>
@@ -8278,7 +8036,7 @@
       <c r="U85" s="6"/>
       <c r="V85" s="6"/>
       <c r="W85" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X85" s="10">
         <f t="shared" si="16"/>
@@ -8289,26 +8047,23 @@
         <f t="shared" si="17"/>
         <v>44571</v>
       </c>
-      <c r="AA85" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA85" s="14"/>
       <c r="AB85" s="14"/>
       <c r="AC85" s="14"/>
-      <c r="AD85" s="14"/>
-      <c r="AE85" s="18"/>
-    </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD85" s="18"/>
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E86" s="6">
         <v>46</v>
@@ -8336,7 +8091,7 @@
       </c>
       <c r="L86" s="6"/>
       <c r="M86" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N86" s="10">
         <v>44490</v>
@@ -8344,7 +8099,7 @@
       <c r="O86" s="16"/>
       <c r="P86" s="36"/>
       <c r="Q86" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R86" s="10">
         <f t="shared" si="14"/>
@@ -8358,7 +8113,7 @@
       <c r="U86" s="6"/>
       <c r="V86" s="6"/>
       <c r="W86" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X86" s="10">
         <f t="shared" si="16"/>
@@ -8369,26 +8124,23 @@
         <f t="shared" si="17"/>
         <v>44602</v>
       </c>
-      <c r="AA86" s="18" t="s">
-        <v>193</v>
-      </c>
+      <c r="AA86" s="14"/>
       <c r="AB86" s="14"/>
       <c r="AC86" s="14"/>
-      <c r="AD86" s="14"/>
-      <c r="AE86" s="18"/>
-    </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD86" s="18"/>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E87" s="6">
         <v>38</v>
@@ -8416,7 +8168,7 @@
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N87" s="10">
         <v>44463</v>
@@ -8424,7 +8176,7 @@
       <c r="O87" s="16"/>
       <c r="P87" s="16"/>
       <c r="Q87" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R87" s="10">
         <f t="shared" si="14"/>
@@ -8438,7 +8190,7 @@
       <c r="U87" s="6"/>
       <c r="V87" s="6"/>
       <c r="W87" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X87" s="10">
         <f t="shared" si="16"/>
@@ -8449,26 +8201,23 @@
         <f t="shared" si="17"/>
         <v>44575</v>
       </c>
-      <c r="AA87" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB87" s="18"/>
+      <c r="AA87" s="18"/>
+      <c r="AB87" s="14"/>
       <c r="AC87" s="14"/>
-      <c r="AD87" s="14"/>
-      <c r="AE87" s="18"/>
-    </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD87" s="18"/>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E88" s="6">
         <v>55</v>
@@ -8496,7 +8245,7 @@
       </c>
       <c r="L88" s="6"/>
       <c r="M88" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N88" s="10">
         <v>44463</v>
@@ -8504,7 +8253,7 @@
       <c r="O88" s="16"/>
       <c r="P88" s="16"/>
       <c r="Q88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R88" s="10">
         <f t="shared" si="14"/>
@@ -8518,7 +8267,7 @@
       <c r="U88" s="6"/>
       <c r="V88" s="6"/>
       <c r="W88" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X88" s="10">
         <f t="shared" si="16"/>
@@ -8529,26 +8278,23 @@
         <f t="shared" si="17"/>
         <v>44575</v>
       </c>
-      <c r="AA88" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB88" s="18"/>
+      <c r="AA88" s="18"/>
+      <c r="AB88" s="14"/>
       <c r="AC88" s="14"/>
-      <c r="AD88" s="14"/>
-      <c r="AE88" s="18"/>
-    </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD88" s="18"/>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E89" s="6">
         <v>27</v>
@@ -8584,7 +8330,7 @@
       <c r="O89" s="16"/>
       <c r="P89" s="36"/>
       <c r="Q89" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R89" s="10">
         <f t="shared" si="14"/>
@@ -8598,7 +8344,7 @@
       <c r="U89" s="6"/>
       <c r="V89" s="6"/>
       <c r="W89" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X89" s="10">
         <f t="shared" si="16"/>
@@ -8609,26 +8355,23 @@
         <f t="shared" si="17"/>
         <v>44602</v>
       </c>
-      <c r="AA89" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA89" s="14"/>
       <c r="AB89" s="14"/>
       <c r="AC89" s="14"/>
-      <c r="AD89" s="14"/>
-      <c r="AE89" s="18"/>
-    </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD89" s="18"/>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E90" s="6">
         <v>27</v>
@@ -8664,7 +8407,7 @@
       <c r="O90" s="16"/>
       <c r="P90" s="36"/>
       <c r="Q90" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R90" s="10">
         <f t="shared" si="14"/>
@@ -8678,7 +8421,7 @@
       <c r="U90" s="6"/>
       <c r="V90" s="6"/>
       <c r="W90" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X90" s="10">
         <f t="shared" si="16"/>
@@ -8689,26 +8432,23 @@
         <f t="shared" si="17"/>
         <v>44602</v>
       </c>
-      <c r="AA90" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA90" s="14"/>
       <c r="AB90" s="14"/>
       <c r="AC90" s="14"/>
-      <c r="AD90" s="14"/>
-      <c r="AE90" s="18"/>
-    </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD90" s="18"/>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E91" s="6">
         <v>50</v>
@@ -8730,7 +8470,7 @@
       </c>
       <c r="L91" s="6"/>
       <c r="M91" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="N91" s="10">
         <v>44462</v>
@@ -8738,7 +8478,7 @@
       <c r="O91" s="16"/>
       <c r="P91" s="16"/>
       <c r="Q91" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R91" s="10">
         <f t="shared" si="14"/>
@@ -8752,7 +8492,7 @@
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
       <c r="W91" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X91" s="10">
         <f t="shared" si="16"/>
@@ -8763,26 +8503,23 @@
         <f t="shared" si="17"/>
         <v>44574</v>
       </c>
-      <c r="AA91" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA91" s="14"/>
       <c r="AB91" s="14"/>
       <c r="AC91" s="14"/>
-      <c r="AD91" s="14"/>
-      <c r="AE91" s="18"/>
-    </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD91" s="18"/>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E92" s="6">
         <v>59</v>
@@ -8810,17 +8547,17 @@
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="N92" s="10">
         <v>44462</v>
       </c>
       <c r="O92" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P92" s="16"/>
       <c r="Q92" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R92" s="10">
         <f t="shared" si="14"/>
@@ -8834,7 +8571,7 @@
       <c r="U92" s="6"/>
       <c r="V92" s="6"/>
       <c r="W92" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X92" s="10">
         <f t="shared" si="16"/>
@@ -8845,26 +8582,23 @@
         <f t="shared" si="17"/>
         <v>44574</v>
       </c>
-      <c r="AA92" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA92" s="14"/>
       <c r="AB92" s="14"/>
       <c r="AC92" s="14"/>
-      <c r="AD92" s="14"/>
-      <c r="AE92" s="18"/>
-    </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD92" s="18"/>
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E93" s="6">
         <v>33</v>
@@ -8892,7 +8626,7 @@
       </c>
       <c r="L93" s="6"/>
       <c r="M93" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N93" s="10">
         <v>44491</v>
@@ -8900,7 +8634,7 @@
       <c r="O93" s="16"/>
       <c r="P93" s="16"/>
       <c r="Q93" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R93" s="10">
         <f t="shared" si="14"/>
@@ -8914,7 +8648,7 @@
       <c r="U93" s="6"/>
       <c r="V93" s="6"/>
       <c r="W93" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X93" s="10">
         <f t="shared" si="16"/>
@@ -8925,26 +8659,23 @@
         <f t="shared" si="17"/>
         <v>44603</v>
       </c>
-      <c r="AA93" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA93" s="14"/>
       <c r="AB93" s="14"/>
       <c r="AC93" s="14"/>
-      <c r="AD93" s="14"/>
-      <c r="AE93" s="18"/>
-    </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD93" s="18"/>
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E94" s="23">
         <v>53</v>
@@ -8966,7 +8697,7 @@
       </c>
       <c r="L94" s="23"/>
       <c r="M94" s="23" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N94" s="25">
         <v>44490</v>
@@ -8974,7 +8705,7 @@
       <c r="O94" s="26"/>
       <c r="P94" s="26"/>
       <c r="Q94" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R94" s="25">
         <f t="shared" si="14"/>
@@ -8988,7 +8719,7 @@
       <c r="U94" s="23"/>
       <c r="V94" s="23"/>
       <c r="W94" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X94" s="25">
         <f t="shared" si="16"/>
@@ -9001,22 +8732,21 @@
       </c>
       <c r="AA94" s="27"/>
       <c r="AB94" s="27"/>
-      <c r="AC94" s="27"/>
-      <c r="AD94" s="23"/>
-      <c r="AE94" s="27"/>
-    </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AC94" s="23"/>
+      <c r="AD94" s="27"/>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E95" s="6">
         <v>54</v>
@@ -9044,7 +8774,7 @@
       </c>
       <c r="L95" s="6"/>
       <c r="M95" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N95" s="10">
         <v>44516</v>
@@ -9052,7 +8782,7 @@
       <c r="O95" s="16"/>
       <c r="P95" s="16"/>
       <c r="Q95" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R95" s="10">
         <f t="shared" si="14"/>
@@ -9066,7 +8796,7 @@
       <c r="U95" s="6"/>
       <c r="V95" s="6"/>
       <c r="W95" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X95" s="10">
         <f t="shared" si="16"/>
@@ -9077,26 +8807,23 @@
         <f t="shared" si="17"/>
         <v>44628</v>
       </c>
-      <c r="AA95" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA95" s="14"/>
       <c r="AB95" s="14"/>
       <c r="AC95" s="14"/>
-      <c r="AD95" s="14"/>
-      <c r="AE95" s="18"/>
-    </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD95" s="18"/>
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E96" s="6">
         <v>57</v>
@@ -9132,7 +8859,7 @@
       <c r="O96" s="16"/>
       <c r="P96" s="16"/>
       <c r="Q96" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R96" s="10">
         <f t="shared" si="14"/>
@@ -9146,7 +8873,7 @@
       <c r="U96" s="6"/>
       <c r="V96" s="6"/>
       <c r="W96" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X96" s="10">
         <f t="shared" si="16"/>
@@ -9157,26 +8884,23 @@
         <f t="shared" si="17"/>
         <v>44602</v>
       </c>
-      <c r="AA96" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA96" s="14"/>
       <c r="AB96" s="14"/>
       <c r="AC96" s="14"/>
-      <c r="AD96" s="14"/>
-      <c r="AE96" s="18"/>
-    </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD96" s="18"/>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E97" s="6">
         <v>32</v>
@@ -9212,7 +8936,7 @@
       <c r="O97" s="16"/>
       <c r="P97" s="16"/>
       <c r="Q97" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R97" s="10">
         <f t="shared" si="14"/>
@@ -9226,7 +8950,7 @@
       <c r="U97" s="6"/>
       <c r="V97" s="6"/>
       <c r="W97" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X97" s="10">
         <f t="shared" si="16"/>
@@ -9237,26 +8961,23 @@
         <f t="shared" si="17"/>
         <v>44603</v>
       </c>
-      <c r="AA97" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA97" s="14"/>
       <c r="AB97" s="14"/>
       <c r="AC97" s="14"/>
-      <c r="AD97" s="14"/>
-      <c r="AE97" s="18"/>
-    </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD97" s="18"/>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E98" s="6">
         <v>33</v>
@@ -9284,7 +9005,7 @@
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N98" s="10">
         <v>44491</v>
@@ -9292,7 +9013,7 @@
       <c r="O98" s="16"/>
       <c r="P98" s="16"/>
       <c r="Q98" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R98" s="10">
         <f t="shared" si="14"/>
@@ -9306,7 +9027,7 @@
       <c r="U98" s="6"/>
       <c r="V98" s="6"/>
       <c r="W98" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X98" s="10">
         <f t="shared" si="16"/>
@@ -9317,26 +9038,23 @@
         <f t="shared" si="17"/>
         <v>44603</v>
       </c>
-      <c r="AA98" s="18" t="s">
-        <v>65</v>
-      </c>
+      <c r="AA98" s="14"/>
       <c r="AB98" s="14"/>
       <c r="AC98" s="14"/>
-      <c r="AD98" s="14"/>
-      <c r="AE98" s="18"/>
-    </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD98" s="18"/>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E99" s="6">
         <v>26</v>
@@ -9372,7 +9090,7 @@
       <c r="O99" s="16"/>
       <c r="P99" s="16"/>
       <c r="Q99" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R99" s="10">
         <f t="shared" si="14"/>
@@ -9386,7 +9104,7 @@
       <c r="U99" s="6"/>
       <c r="V99" s="6"/>
       <c r="W99" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X99" s="10">
         <f t="shared" si="16"/>
@@ -9397,26 +9115,23 @@
         <f t="shared" si="17"/>
         <v>44600</v>
       </c>
-      <c r="AA99" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA99" s="14"/>
       <c r="AB99" s="14"/>
       <c r="AC99" s="14"/>
-      <c r="AD99" s="14"/>
-      <c r="AE99" s="18"/>
-    </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD99" s="18"/>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E100" s="6">
         <v>22</v>
@@ -9444,7 +9159,7 @@
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N100" s="10">
         <v>44489</v>
@@ -9452,7 +9167,7 @@
       <c r="O100" s="16"/>
       <c r="P100" s="16"/>
       <c r="Q100" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R100" s="10">
         <f t="shared" si="14"/>
@@ -9466,7 +9181,7 @@
       <c r="U100" s="6"/>
       <c r="V100" s="6"/>
       <c r="W100" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X100" s="10">
         <f t="shared" si="16"/>
@@ -9477,26 +9192,23 @@
         <f t="shared" si="17"/>
         <v>44601</v>
       </c>
-      <c r="AA100" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB100" s="6"/>
+      <c r="AA100" s="6"/>
+      <c r="AB100" s="14"/>
       <c r="AC100" s="14"/>
-      <c r="AD100" s="14"/>
-      <c r="AE100" s="18"/>
-    </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD100" s="18"/>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E101" s="6">
         <v>48</v>
@@ -9532,7 +9244,7 @@
       <c r="O101" s="16"/>
       <c r="P101" s="16"/>
       <c r="Q101" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R101" s="10">
         <f t="shared" si="14"/>
@@ -9546,7 +9258,7 @@
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
       <c r="W101" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X101" s="10">
         <f t="shared" si="16"/>
@@ -9557,26 +9269,23 @@
         <f t="shared" si="17"/>
         <v>44606</v>
       </c>
-      <c r="AA101" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA101" s="14"/>
       <c r="AB101" s="14"/>
       <c r="AC101" s="14"/>
-      <c r="AD101" s="14"/>
-      <c r="AE101" s="18"/>
-    </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD101" s="18"/>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E102" s="6">
         <v>29</v>
@@ -9607,10 +9316,10 @@
       <c r="N102" s="6"/>
       <c r="O102" s="6"/>
       <c r="P102" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R102" s="10">
         <v>44280</v>
@@ -9622,7 +9331,7 @@
       <c r="U102" s="6"/>
       <c r="V102" s="6"/>
       <c r="W102" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X102" s="10">
         <v>44336</v>
@@ -9631,26 +9340,23 @@
       <c r="Z102" s="10">
         <v>44364</v>
       </c>
-      <c r="AA102" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA102" s="14"/>
       <c r="AB102" s="14"/>
       <c r="AC102" s="14"/>
       <c r="AD102" s="14"/>
-      <c r="AE102" s="14"/>
-    </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E103" s="6">
         <v>46</v>
@@ -9684,7 +9390,7 @@
       <c r="O103" s="16"/>
       <c r="P103" s="16"/>
       <c r="Q103" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R103" s="10">
         <f t="shared" ref="R103:R120" si="18">N103+28</f>
@@ -9697,7 +9403,7 @@
       <c r="U103" s="6"/>
       <c r="V103" s="6"/>
       <c r="W103" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X103" s="10">
         <v>44572</v>
@@ -9707,26 +9413,23 @@
         <f>X103+28</f>
         <v>44600</v>
       </c>
-      <c r="AA103" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA103" s="14"/>
       <c r="AB103" s="14"/>
       <c r="AC103" s="14"/>
-      <c r="AD103" s="14"/>
-      <c r="AE103" s="18"/>
-    </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD103" s="18"/>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E104" s="6">
         <v>53</v>
@@ -9754,7 +9457,7 @@
       </c>
       <c r="L104" s="6"/>
       <c r="M104" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N104" s="10">
         <v>44496</v>
@@ -9762,7 +9465,7 @@
       <c r="O104" s="16"/>
       <c r="P104" s="16"/>
       <c r="Q104" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R104" s="10">
         <f t="shared" si="18"/>
@@ -9776,7 +9479,7 @@
       <c r="U104" s="6"/>
       <c r="V104" s="6"/>
       <c r="W104" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X104" s="15">
         <v>44222</v>
@@ -9786,26 +9489,23 @@
         <f t="shared" ref="Z104:Z120" si="20">X104+28</f>
         <v>44250</v>
       </c>
-      <c r="AA104" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA104" s="14"/>
       <c r="AB104" s="14"/>
       <c r="AC104" s="14"/>
-      <c r="AD104" s="14"/>
-      <c r="AE104" s="18"/>
-    </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD104" s="18"/>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E105" s="6">
         <v>24</v>
@@ -9833,7 +9533,7 @@
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N105" s="10">
         <v>44496</v>
@@ -9841,7 +9541,7 @@
       <c r="O105" s="16"/>
       <c r="P105" s="16"/>
       <c r="Q105" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R105" s="10">
         <f t="shared" si="18"/>
@@ -9855,7 +9555,7 @@
       <c r="U105" s="6"/>
       <c r="V105" s="6"/>
       <c r="W105" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X105" s="10">
         <f t="shared" ref="X105:X120" si="21">T105+28</f>
@@ -9866,26 +9566,23 @@
         <f t="shared" si="20"/>
         <v>44608</v>
       </c>
-      <c r="AA105" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA105" s="14"/>
       <c r="AB105" s="14"/>
       <c r="AC105" s="14"/>
-      <c r="AD105" s="14"/>
-      <c r="AE105" s="18"/>
-    </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD105" s="18"/>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E106" s="6">
         <v>65</v>
@@ -9905,7 +9602,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N106" s="10">
         <v>44497</v>
@@ -9913,7 +9610,7 @@
       <c r="O106" s="16"/>
       <c r="P106" s="16"/>
       <c r="Q106" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R106" s="10">
         <f t="shared" si="18"/>
@@ -9927,7 +9624,7 @@
       <c r="U106" s="6"/>
       <c r="V106" s="6"/>
       <c r="W106" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X106" s="10">
         <f t="shared" si="21"/>
@@ -9938,26 +9635,23 @@
         <f t="shared" si="20"/>
         <v>44609</v>
       </c>
-      <c r="AA106" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA106" s="14"/>
       <c r="AB106" s="14"/>
       <c r="AC106" s="14"/>
-      <c r="AD106" s="14"/>
-      <c r="AE106" s="18"/>
-    </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD106" s="18"/>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E107" s="6">
         <v>55</v>
@@ -9985,7 +9679,7 @@
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N107" s="10">
         <v>44515</v>
@@ -9993,7 +9687,7 @@
       <c r="O107" s="16"/>
       <c r="P107" s="16"/>
       <c r="Q107" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R107" s="10">
         <f t="shared" si="18"/>
@@ -10007,7 +9701,7 @@
       <c r="U107" s="6"/>
       <c r="V107" s="6"/>
       <c r="W107" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X107" s="10">
         <f t="shared" si="21"/>
@@ -10018,26 +9712,23 @@
         <f t="shared" si="20"/>
         <v>44627</v>
       </c>
-      <c r="AA107" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA107" s="14"/>
       <c r="AB107" s="14"/>
       <c r="AC107" s="14"/>
-      <c r="AD107" s="14"/>
-      <c r="AE107" s="18"/>
-    </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD107" s="18"/>
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E108" s="6">
         <v>28</v>
@@ -10065,7 +9756,7 @@
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N108" s="10">
         <v>44523</v>
@@ -10073,7 +9764,7 @@
       <c r="O108" s="16"/>
       <c r="P108" s="16"/>
       <c r="Q108" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R108" s="10">
         <f t="shared" si="18"/>
@@ -10086,7 +9777,7 @@
       <c r="U108" s="6"/>
       <c r="V108" s="6"/>
       <c r="W108" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X108" s="10">
         <f t="shared" si="21"/>
@@ -10097,26 +9788,23 @@
         <f t="shared" si="20"/>
         <v>44631</v>
       </c>
-      <c r="AA108" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA108" s="14"/>
       <c r="AB108" s="14"/>
       <c r="AC108" s="14"/>
-      <c r="AD108" s="14"/>
-      <c r="AE108" s="6"/>
-    </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD108" s="6"/>
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C109" s="23" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E109" s="23">
         <v>60</v>
@@ -10136,7 +9824,7 @@
       <c r="K109" s="24"/>
       <c r="L109" s="23"/>
       <c r="M109" s="23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N109" s="25">
         <v>44517</v>
@@ -10144,7 +9832,7 @@
       <c r="O109" s="26"/>
       <c r="P109" s="26"/>
       <c r="Q109" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R109" s="25">
         <f t="shared" si="18"/>
@@ -10158,7 +9846,7 @@
       <c r="U109" s="23"/>
       <c r="V109" s="23"/>
       <c r="W109" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X109" s="25">
         <f t="shared" si="21"/>
@@ -10173,20 +9861,19 @@
       <c r="AB109" s="27"/>
       <c r="AC109" s="27"/>
       <c r="AD109" s="27"/>
-      <c r="AE109" s="27"/>
-    </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E110" s="6">
         <v>21</v>
@@ -10214,7 +9901,7 @@
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N110" s="10">
         <v>44515</v>
@@ -10222,7 +9909,7 @@
       <c r="O110" s="16"/>
       <c r="P110" s="16"/>
       <c r="Q110" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R110" s="10">
         <f t="shared" si="18"/>
@@ -10236,7 +9923,7 @@
       <c r="U110" s="6"/>
       <c r="V110" s="6"/>
       <c r="W110" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X110" s="10">
         <f t="shared" si="21"/>
@@ -10247,26 +9934,23 @@
         <f t="shared" si="20"/>
         <v>44627</v>
       </c>
-      <c r="AA110" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA110" s="14"/>
       <c r="AB110" s="14"/>
       <c r="AC110" s="14"/>
-      <c r="AD110" s="14"/>
-      <c r="AE110" s="18"/>
-    </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD110" s="18"/>
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E111" s="6">
         <v>52</v>
@@ -10286,7 +9970,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="6"/>
       <c r="M111" s="11" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N111" s="10">
         <v>44517</v>
@@ -10294,7 +9978,7 @@
       <c r="O111" s="16"/>
       <c r="P111" s="16"/>
       <c r="Q111" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R111" s="10">
         <f t="shared" si="18"/>
@@ -10308,7 +9992,7 @@
       <c r="U111" s="6"/>
       <c r="V111" s="6"/>
       <c r="W111" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X111" s="10">
         <f t="shared" si="21"/>
@@ -10319,26 +10003,23 @@
         <f t="shared" si="20"/>
         <v>44629</v>
       </c>
-      <c r="AA111" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA111" s="14"/>
       <c r="AB111" s="14"/>
       <c r="AC111" s="14"/>
-      <c r="AD111" s="14"/>
-      <c r="AE111" s="18"/>
-    </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD111" s="18"/>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E112" s="23">
         <v>27</v>
@@ -10358,7 +10039,7 @@
       <c r="K112" s="24"/>
       <c r="L112" s="23"/>
       <c r="M112" s="28" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N112" s="25">
         <v>44516</v>
@@ -10366,7 +10047,7 @@
       <c r="O112" s="26"/>
       <c r="P112" s="26"/>
       <c r="Q112" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R112" s="25">
         <f t="shared" si="18"/>
@@ -10380,7 +10061,7 @@
       <c r="U112" s="23"/>
       <c r="V112" s="23"/>
       <c r="W112" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X112" s="25">
         <f t="shared" si="21"/>
@@ -10395,20 +10076,19 @@
       <c r="AB112" s="23"/>
       <c r="AC112" s="23"/>
       <c r="AD112" s="23"/>
-      <c r="AE112" s="23"/>
-    </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E113" s="6">
         <v>25</v>
@@ -10436,7 +10116,7 @@
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="N113" s="10">
         <v>44550</v>
@@ -10444,7 +10124,7 @@
       <c r="O113" s="16"/>
       <c r="P113" s="16"/>
       <c r="Q113" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R113" s="10">
         <f t="shared" si="18"/>
@@ -10458,7 +10138,7 @@
       <c r="U113" s="6"/>
       <c r="V113" s="6"/>
       <c r="W113" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X113" s="10">
         <f t="shared" si="21"/>
@@ -10469,26 +10149,23 @@
         <f t="shared" si="20"/>
         <v>44662</v>
       </c>
-      <c r="AA113" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA113" s="14"/>
       <c r="AB113" s="14"/>
       <c r="AC113" s="14"/>
-      <c r="AD113" s="14"/>
-      <c r="AE113" s="18"/>
-    </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD113" s="18"/>
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E114" s="6">
         <v>41</v>
@@ -10512,7 +10189,7 @@
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N114" s="10">
         <v>44547</v>
@@ -10520,7 +10197,7 @@
       <c r="O114" s="16"/>
       <c r="P114" s="16"/>
       <c r="Q114" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R114" s="10">
         <f t="shared" si="18"/>
@@ -10534,7 +10211,7 @@
       <c r="U114" s="6"/>
       <c r="V114" s="6"/>
       <c r="W114" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X114" s="15">
         <f>T114+42</f>
@@ -10545,26 +10222,23 @@
         <f t="shared" si="20"/>
         <v>44673</v>
       </c>
-      <c r="AA114" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA114" s="14"/>
       <c r="AB114" s="14"/>
       <c r="AC114" s="14"/>
-      <c r="AD114" s="14"/>
-      <c r="AE114" s="18"/>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD114" s="18"/>
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E115" s="6">
         <v>35</v>
@@ -10592,7 +10266,7 @@
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N115" s="10">
         <v>44545</v>
@@ -10600,7 +10274,7 @@
       <c r="O115" s="16"/>
       <c r="P115" s="16"/>
       <c r="Q115" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R115" s="10">
         <f t="shared" si="18"/>
@@ -10614,7 +10288,7 @@
       <c r="U115" s="6"/>
       <c r="V115" s="6"/>
       <c r="W115" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X115" s="10">
         <f t="shared" si="21"/>
@@ -10625,26 +10299,23 @@
         <f t="shared" si="20"/>
         <v>44657</v>
       </c>
-      <c r="AA115" s="14" t="s">
-        <v>29</v>
-      </c>
+      <c r="AA115" s="14"/>
       <c r="AB115" s="14"/>
       <c r="AC115" s="14"/>
-      <c r="AD115" s="14"/>
-      <c r="AE115" s="18"/>
-    </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD115" s="18"/>
+    </row>
+    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D116" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E116" s="23">
         <v>56</v>
@@ -10664,7 +10335,7 @@
       <c r="K116" s="24"/>
       <c r="L116" s="23"/>
       <c r="M116" s="28" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N116" s="25">
         <v>44551</v>
@@ -10672,7 +10343,7 @@
       <c r="O116" s="26"/>
       <c r="P116" s="26"/>
       <c r="Q116" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R116" s="25">
         <f t="shared" si="18"/>
@@ -10686,7 +10357,7 @@
       <c r="U116" s="23"/>
       <c r="V116" s="23"/>
       <c r="W116" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X116" s="25">
         <f t="shared" si="21"/>
@@ -10701,20 +10372,19 @@
       <c r="AB116" s="27"/>
       <c r="AC116" s="27"/>
       <c r="AD116" s="27"/>
-      <c r="AE116" s="27"/>
-    </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E117" s="6">
         <v>32</v>
@@ -10742,7 +10412,7 @@
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N117" s="10">
         <v>44547</v>
@@ -10750,7 +10420,7 @@
       <c r="O117" s="16"/>
       <c r="P117" s="16"/>
       <c r="Q117" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R117" s="10">
         <f t="shared" si="18"/>
@@ -10764,7 +10434,7 @@
       <c r="U117" s="6"/>
       <c r="V117" s="6"/>
       <c r="W117" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X117" s="10">
         <f t="shared" si="21"/>
@@ -10775,26 +10445,23 @@
         <f t="shared" si="20"/>
         <v>44659</v>
       </c>
-      <c r="AA117" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB117" s="6"/>
+      <c r="AA117" s="6"/>
+      <c r="AB117" s="14"/>
       <c r="AC117" s="14"/>
-      <c r="AD117" s="14"/>
-      <c r="AE117" s="18"/>
-    </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD117" s="18"/>
+    </row>
+    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E118" s="6">
         <v>53</v>
@@ -10822,7 +10489,7 @@
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N118" s="10">
         <v>44552</v>
@@ -10830,7 +10497,7 @@
       <c r="O118" s="16"/>
       <c r="P118" s="16"/>
       <c r="Q118" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R118" s="10">
         <f t="shared" si="18"/>
@@ -10844,7 +10511,7 @@
       <c r="U118" s="6"/>
       <c r="V118" s="6"/>
       <c r="W118" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X118" s="10">
         <f t="shared" si="21"/>
@@ -10855,26 +10522,23 @@
         <f t="shared" si="20"/>
         <v>44664</v>
       </c>
-      <c r="AA118" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB118" s="6"/>
+      <c r="AA118" s="6"/>
+      <c r="AB118" s="14"/>
       <c r="AC118" s="14"/>
-      <c r="AD118" s="14"/>
-      <c r="AE118" s="18"/>
-    </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD118" s="18"/>
+    </row>
+    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E119" s="6">
         <v>60</v>
@@ -10908,7 +10572,7 @@
       <c r="O119" s="16"/>
       <c r="P119" s="16"/>
       <c r="Q119" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R119" s="10">
         <f t="shared" si="18"/>
@@ -10922,7 +10586,7 @@
       <c r="U119" s="6"/>
       <c r="V119" s="6"/>
       <c r="W119" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X119" s="10">
         <f t="shared" si="21"/>
@@ -10933,26 +10597,23 @@
         <f t="shared" si="20"/>
         <v>44672</v>
       </c>
-      <c r="AA119" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB119" s="14"/>
+      <c r="AA119" s="14"/>
+      <c r="AB119" s="18"/>
       <c r="AC119" s="18"/>
       <c r="AD119" s="18"/>
-      <c r="AE119" s="18"/>
-    </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E120" s="6">
         <v>20</v>
@@ -10986,7 +10647,7 @@
       <c r="O120" s="16"/>
       <c r="P120" s="16"/>
       <c r="Q120" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R120" s="10">
         <f t="shared" si="18"/>
@@ -11000,7 +10661,7 @@
       <c r="U120" s="6"/>
       <c r="V120" s="6"/>
       <c r="W120" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X120" s="10">
         <f t="shared" si="21"/>
@@ -11011,82 +10672,79 @@
         <f t="shared" si="20"/>
         <v>44665</v>
       </c>
-      <c r="AA120" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB120" s="6"/>
+      <c r="AA120" s="6"/>
+      <c r="AB120" s="14"/>
       <c r="AC120" s="14"/>
-      <c r="AD120" s="14"/>
-      <c r="AE120" s="18"/>
-    </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AD120" s="18"/>
+    </row>
+    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B121" s="37" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>4</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A123" s="39" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G123" s="43" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
       <c r="J123" s="43"/>
       <c r="K123" s="43"/>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A124" s="40" t="s">
         <v>13</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G124" s="41" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H124" s="41"/>
       <c r="I124" s="41"/>
       <c r="J124" s="41"/>
       <c r="K124" s="41"/>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A125" s="39" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A126" s="40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
